--- a/05_Figures/F06_prediction/proteins/T3/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_1rm_legpress/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -134,360 +134,390 @@
     <t xml:space="preserve">ATP2A2</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPS22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMPCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA2D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPZ1</t>
+  </si>
+  <si>
     <t xml:space="preserve">DDT</t>
   </si>
   <si>
+    <t xml:space="preserve">DENR</t>
+  </si>
+  <si>
     <t xml:space="preserve">EIF5B</t>
   </si>
   <si>
-    <t xml:space="preserve">MRPS22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PMPCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNA2D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENR</t>
-  </si>
-  <si>
     <t xml:space="preserve">GARS1</t>
   </si>
   <si>
+    <t xml:space="preserve">GLUD1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MSRB2</t>
   </si>
   <si>
+    <t xml:space="preserve">PRKAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAR2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XRCC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS18B</t>
+  </si>
+  <si>
     <t xml:space="preserve">PIN4</t>
   </si>
   <si>
     <t xml:space="preserve">PPIL1</t>
   </si>
   <si>
-    <t xml:space="preserve">PRKAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAR2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XRCC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS1</t>
+    <t xml:space="preserve">NT5C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2D1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHORDC1</t>
   </si>
   <si>
     <t xml:space="preserve">FBLN5</t>
   </si>
   <si>
-    <t xml:space="preserve">GLUD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHORDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2D1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD36</t>
+    <t xml:space="preserve">GPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEDD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDCD6IP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPME1</t>
   </si>
   <si>
     <t xml:space="preserve">COPS2</t>
   </si>
   <si>
-    <t xml:space="preserve">GPT</t>
+    <t xml:space="preserve">DAD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYPL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FYCO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUDT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAMPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ART3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA1S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGLUCY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYPC</t>
   </si>
   <si>
     <t xml:space="preserve">HDDC2</t>
   </si>
   <si>
-    <t xml:space="preserve">MRPS18B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEDD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDCD6IP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ART3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FYCO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAMPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYPL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGLUCY</t>
+    <t xml:space="preserve">HDHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISCU</t>
   </si>
   <si>
     <t xml:space="preserve">LANCL1</t>
   </si>
   <si>
+    <t xml:space="preserve">MGST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AAMDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERP44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHPT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB9A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPY2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COL6A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX3X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMAC2L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSK3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3-3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HUWE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SURF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIMM10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBXN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANKRD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAV2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX4I1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSNK2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPRS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPS15L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERP29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAHD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAPDHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPHN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GYS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IQGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2HGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYRM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTPN</t>
+  </si>
+  <si>
     <t xml:space="preserve">MYH4</t>
   </si>
   <si>
-    <t xml:space="preserve">AAMDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RDX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNA1S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERP44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HUWE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IARS2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHPT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB9A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL6A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX3X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMAC2L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSK3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3-3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SURF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBXN6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACOT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANKRD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNPY2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COL6A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX4I1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSNK2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPRS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPS15L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERP29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAHD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLOD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPHN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IQGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JSRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAN2C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTPN</t>
-  </si>
-  <si>
     <t xml:space="preserve">NAXE</t>
   </si>
   <si>
+    <t xml:space="preserve">NDUFS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIBAN1</t>
+  </si>
+  <si>
     <t xml:space="preserve">NNT</t>
   </si>
   <si>
@@ -506,6 +536,9 @@
     <t xml:space="preserve">PFDN6</t>
   </si>
   <si>
+    <t xml:space="preserve">PFKFB2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PHB2</t>
   </si>
   <si>
@@ -518,6 +551,9 @@
     <t xml:space="preserve">PLCL2</t>
   </si>
   <si>
+    <t xml:space="preserve">PMPCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">PPCS</t>
   </si>
   <si>
@@ -548,16 +584,16 @@
     <t xml:space="preserve">SH3BGR</t>
   </si>
   <si>
-    <t xml:space="preserve">STIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUGT1</t>
+    <t xml:space="preserve">SLMAP</t>
   </si>
   <si>
     <t xml:space="preserve">TARS1</t>
   </si>
   <si>
-    <t xml:space="preserve">TIMM10</t>
+    <t xml:space="preserve">TMED9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPPP</t>
   </si>
   <si>
     <t xml:space="preserve">TRMT112</t>
@@ -566,10 +602,10 @@
     <t xml:space="preserve">TSN</t>
   </si>
   <si>
+    <t xml:space="preserve">TUBA8</t>
+  </si>
+  <si>
     <t xml:space="preserve">TXLNB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBL5</t>
   </si>
 </sst>
 </file>
@@ -956,16 +992,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.37482249769929</v>
+        <v>-1.29183453119482</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.543503222525638</v>
+        <v>-0.525565822442283</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -989,29 +1025,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.37482249769929</v>
+        <v>-1.29183453119482</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.543503222525638</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.825870646766169</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.82089552238806</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.729162767153619</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.719007115249648</v>
-      </c>
+        <v>-0.525565822442283</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1035,2206 +1063,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-3.65939028451863</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.216385620473241</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.669830571231576</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.545087228734112</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.547084374053959</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-1.85823460561022</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.522727745413782</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-1.35430689054814</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.00466939643091102</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.06764400078874</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.52779234014397</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-1.12207987887511</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.00284920342908324</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.774019003797029</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.616473642767538</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.56777451953791</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.557342623068305</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-2.03229076357405</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.965953533413441</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.318501222452621</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.46380798005988</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.00589048682682</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.0161765719465234</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.357216115082702</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.109838590369844</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.645312501120914</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.572363343465034</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.588505313998053</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.582470290273057</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.501795592458394</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-2.14255101355123</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.67601286260206</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.289907893573087</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.212287827061483</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-1.17334918807057</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.0826192720089289</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.293829490075856</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.130206670708226</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.0200701174680284</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.548379731996608</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.88858622964493</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.00361309858611225</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.171790761179724</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.248896625239833</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0.316820422890802</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0.15712103477205</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.108699485971972</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.394600701779688</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.22125188243335</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.958428967907122</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.78037804405965</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.637145412814852</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.26667162515159</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.08279484027497</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.49755977382016</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.895356429726734</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.35448876089333</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-2.31838171748846</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0302187156101711</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.995457788101531</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.501129223772689</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.466586752691988</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-2.67946116808587</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.0676782388181112</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-1.14433472021106</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.0946274419153823</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-2.28191335984668</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.635878387575572</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.0476106689761678</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.0611736428652825</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.32056703697031</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.59806818106768</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.482644677316768</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.541807489272802</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.754560229921462</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.36424666769869</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.34889625642885</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.77049513034375</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.509430906679754</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.132177794039269</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.29413834894047</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.0108906744894974</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.917283793277741</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.269470899033021</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.582024647423226</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>0.140831645167961</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.45961287096305</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.210413646296282</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-2.34207865810007</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.413299319752994</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.564581453110935</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.43541148041503</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-2.15740795372379</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.22794925864134</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.650569700469671</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.366497727744007</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-1.92251578699962</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.188803681481428</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.188820886865431</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.673405217844605</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.877579982710365</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.286864368771397</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.103255648569412</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.0760973935357095</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.17457202680666</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.455681735572309</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.849787046573126</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.381596631092052</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.230153413835316</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.872298029563003</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.489052753905836</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.711828257534668</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.0748151247233797</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-1.95253330124936</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.219162257622263</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.71235123120908</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.215196396399282</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.353044906732376</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.736996878797982</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.746518872990232</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.9340264783931</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.10412003725218</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.80641857063172</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.898314340684874</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>0.201756870309849</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.265482591385797</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-1.63891454482622</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.774650437321781</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.09570978154576</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.340260724722202</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.76663839347519</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.717604666668568</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.187963311477073</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.499723862523474</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-2.47773032334333</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0.525225493887897</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.920314142884548</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.663445601942737</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.0924097608556713</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.141430089461594</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-1.52991003455358</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.116496352083476</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.324078706599188</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-1.21493056421313</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.443284915941784</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.547401357199977</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>0.389661522962261</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.451147053539013</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.63544094019394</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.530695758880166</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-1.35227565503111</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-1.40943566717506</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.353302130146444</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-2.20781487026329</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0.302611112728981</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-1.38823598938437</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-3.04548525610839</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.01946528542212</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-0.766036806320554</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.26514567228218</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.416594096258397</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.569899501609429</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.349435926940675</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.409324880659589</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.875480597965061</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.745043715039308</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-1.26111850058719</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.48806573978836</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.465834662161883</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.92933469848603</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.17246677601156</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.238432710333023</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.41299860691126</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.121339824452317</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.349924064234133</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.208417511923311</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-0.209336969363576</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.102633431633632</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.793524284934948</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.202215700685497</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.745688930026696</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.42860907527273</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>0.223166993459145</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.27848109928691</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.0440079482362583</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.08244750445478</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.677410271882296</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.82194895713591</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.365500634878652</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.205951243418346</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.370834704733567</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.264958265093113</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.559431718430933</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.574367256820023</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.836119511852996</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.55044108083739</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.810448564293222</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.53661419320453</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.416036507899948</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.323085773179378</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3277,7 +1105,7 @@
         <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>29.8173223945776</v>
+        <v>30.5642022135617</v>
       </c>
     </row>
     <row r="3">
@@ -3294,7 +1122,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>26.0177709255199</v>
+        <v>32.5383033092442</v>
       </c>
     </row>
     <row r="4">
@@ -3311,7 +1139,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>31.5804232820662</v>
+        <v>31.9191064156496</v>
       </c>
     </row>
     <row r="5">
@@ -3328,7 +1156,7 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>61.6292364631277</v>
+        <v>60.6274556361859</v>
       </c>
     </row>
     <row r="6">
@@ -3345,7 +1173,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>60.0815367735621</v>
+        <v>55.8115328022087</v>
       </c>
     </row>
     <row r="7">
@@ -3362,7 +1190,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>44.3560365770778</v>
+        <v>44.004978141162</v>
       </c>
     </row>
     <row r="8">
@@ -3379,7 +1207,7 @@
         <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>89.0552683682424</v>
+        <v>89.179353716336</v>
       </c>
     </row>
     <row r="9">
@@ -3396,7 +1224,7 @@
         <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>22.5502755499409</v>
+        <v>21.2316784578243</v>
       </c>
     </row>
     <row r="10">
@@ -3413,7 +1241,7 @@
         <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>28.4004044117616</v>
+        <v>29.9408847675779</v>
       </c>
     </row>
     <row r="11">
@@ -3430,7 +1258,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>51.7756450749955</v>
+        <v>53.0649573034643</v>
       </c>
     </row>
     <row r="12">
@@ -3447,7 +1275,7 @@
         <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>55.0004140860135</v>
+        <v>55.6681302084083</v>
       </c>
     </row>
     <row r="13">
@@ -3464,7 +1292,7 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>73.4616161080141</v>
+        <v>71.8929759286384</v>
       </c>
     </row>
     <row r="14">
@@ -3481,7 +1309,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>52.8791098672271</v>
+        <v>54.0611165015625</v>
       </c>
     </row>
     <row r="15">
@@ -3498,7 +1326,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>40.2394289853388</v>
+        <v>40.4498892325323</v>
       </c>
     </row>
     <row r="16">
@@ -3515,7 +1343,7 @@
         <v>89</v>
       </c>
       <c r="E16" t="n">
-        <v>0.981508486398816</v>
+        <v>1.23591765372277</v>
       </c>
     </row>
   </sheetData>
@@ -3557,10 +1385,10 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3574,10 +1402,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3591,10 +1419,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3642,10 +1470,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3659,10 +1487,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -3676,10 +1504,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3693,10 +1521,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3710,10 +1538,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3727,10 +1555,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -3744,10 +1572,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -3761,10 +1589,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +1606,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3795,10 +1623,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3812,10 +1640,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3846,10 +1674,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3863,10 +1691,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
@@ -3880,10 +1708,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="22">
@@ -3897,10 +1725,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="23">
@@ -3914,10 +1742,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -3931,10 +1759,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -3948,10 +1776,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3982,10 +1810,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -3999,10 +1827,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -4135,10 +1963,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -4186,10 +2014,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="40">
@@ -4203,10 +2031,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -4339,10 +2167,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -4441,10 +2269,10 @@
         <v>90</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="55">
@@ -4458,10 +2286,10 @@
         <v>91</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="56">
@@ -4475,10 +2303,10 @@
         <v>92</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="57">
@@ -4492,10 +2320,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -4509,10 +2337,10 @@
         <v>94</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="59">
@@ -4526,10 +2354,10 @@
         <v>95</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -4917,10 +2745,10 @@
         <v>118</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -4934,10 +2762,10 @@
         <v>119</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="84">
@@ -4951,10 +2779,10 @@
         <v>120</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="85">
@@ -4968,10 +2796,10 @@
         <v>121</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="86">
@@ -6042,6 +3870,210 @@
         <v>1</v>
       </c>
       <c r="E148" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="s">
+        <v>185</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="s">
+        <v>186</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="s">
+        <v>187</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>188</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="s">
+        <v>189</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="s">
+        <v>190</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="s">
+        <v>191</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="s">
+        <v>192</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>194</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="s">
+        <v>195</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T3/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T3/d_1rm_legpress/spls/c_data/results.xlsx
@@ -1028,7 +1028,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.29183453119482</v>
@@ -1036,10 +1036,18 @@
       <c r="I3" t="n">
         <v>-0.525565822442283</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.82089552238806</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.825870646766169</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.71186978255025</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.667050116008642</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1063,6 +1071,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.789722633265515</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.937306497297926</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.75404915068983</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.673092609273303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.678466292193937</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.90364780148278</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.739200433382657</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-1.201734061655</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0175068334163372</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.06730805774322</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.59166209174545</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.14467516265512</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.131067055402628</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.71698163875934</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.560853823241695</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.14266191982926</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.522399405241601</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-2.15618569042282</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.749843276569785</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0727904162804931</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.58739057918835</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.656854556541769</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0203230406013246</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.50817589972589</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.14310320541674</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.900444020500637</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.676475373905198</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.571683792419495</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.521795411117194</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.302102620892487</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-2.26167136321283</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-1.77288793161777</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.189849248193077</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.200985686517563</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-1.07060263933215</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.0107741676088582</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.283186675660245</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0312971668999603</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.00440838008146371</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.531764290380787</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.847915288202011</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0142543519681642</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.226539778362568</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.486211453290816</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.343203893205707</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.225335728214398</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.144456364608283</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.605061246616108</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.13797361416991</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.80104983692818</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.64289933502951</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.529124900050224</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.28698575334438</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-1.09095926489569</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.342559037165839</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.823399247467551</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.20140667872017</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-2.31700305416734</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.0302312796472957</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-1.01547263424446</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.466067293351382</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.383146034106819</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.29534452062932</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.00419269412195744</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-1.1666511929517</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.132597163461399</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-2.09362924147299</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.644778827359409</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.124673383389523</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.12371775652807</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.33133130223196</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.671165634709973</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.745046073803849</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.678128127366136</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.936898964622613</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.752235805351686</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-1.27756275623688</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.72707644631943</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.416776738027718</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.222420774845507</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.919450910719756</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.00953411863663045</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.969464048700899</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.408156775399316</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.539239365839042</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.293560496169887</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.58893341928029</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.338159550800693</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.28087904894023</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.341634551812028</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.535380057587699</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.492562794754925</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-2.25568595777749</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.900250169184407</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.505412461674056</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.427751923659325</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-1.56717122545463</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.0195791080081235</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.189068204474352</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.580582593819727</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.88442999136175</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.382128648056391</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.606703252821019</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.164325423672166</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.11000812930842</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.392509455410419</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.67707665895355</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.407919153476866</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.131948878434077</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.722330623181013</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.518225230481433</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.641121478420679</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.14705830078567</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-1.80497987856632</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.279863094390133</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.69703005518867</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.219918467623158</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.046067789201735</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.887269786542997</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.05929550112221</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-2.12462790141154</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.13034528894127</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.05807779111056</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.727606289155408</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.205602359061893</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.211887522921153</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-1.76525749441927</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.958783618427936</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-3.41432199157868</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.357353023865339</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.82271883135842</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.889727031607273</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.243660702033608</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.565050428670393</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-2.35321477063264</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.527212613854362</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.03212535480665</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.84179684012283</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.0811169433220751</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.171287223693347</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.50093221157957</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.119748567732582</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.312465841388191</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-1.42830359371565</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-0.404691365377118</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.570166709227122</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.31309722188344</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.443668200324583</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.52956989172981</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.390988371134683</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.40018179250348</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-1.29166054265292</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.422037761863804</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.7010064841055</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.275066680272711</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.60361642499932</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-1.52597910955911</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.29950767620803</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-0.66320590392368</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.2481878150914</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.296616868753477</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.517737442736609</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.374506134830858</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.431541504807248</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.800512441060941</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.668262260638532</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.941291078091477</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.4900920268124</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.557722766244442</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.03526556895726</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.16300098460512</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.430106233143622</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.482596288670058</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.0769084578181969</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.533648998647549</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.167565432498921</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-0.240505044731487</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.0726003842638445</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.801581448082203</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.221057482199603</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-1.08987457865075</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.32414239114866</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.411704663717134</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-1.6626148429939</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.119758685796574</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.13100203834273</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.711471895078604</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.82235599795431</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.462683961512601</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.0746449611273049</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.418105469781402</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.493661061180104</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.896178137283666</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1.06515697212191</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.939408426887863</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.02739293915283</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.179124788672301</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.43276297667973</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.261438114089216</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.223121583523969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
